--- a/docs/StructureDefinition-mission-timeline-plan.xlsx
+++ b/docs/StructureDefinition-mission-timeline-plan.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.6</t>
+    <t>0.5.8</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-30T19:11:20-07:00</t>
+    <t>2026-02-02T11:11:20-06:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-mission-timeline-plan.xlsx
+++ b/docs/StructureDefinition-mission-timeline-plan.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.8</t>
+    <t>0.5.9</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T11:11:20-06:00</t>
+    <t>2026-02-04T10:26:00-06:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-mission-timeline-plan.xlsx
+++ b/docs/StructureDefinition-mission-timeline-plan.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.12</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T00:24:16-05:00</t>
+    <t>2026-05-25T15:07:02-06:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -456,7 +456,7 @@
     <t>Mission Context</t>
   </si>
   <si>
-    <t>Links radiation exposure to specific space missions</t>
+    <t>Links clinical observations and events to specific space missions</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1

--- a/docs/StructureDefinition-mission-timeline-plan.xlsx
+++ b/docs/StructureDefinition-mission-timeline-plan.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.6.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:07:02-06:00</t>
+    <t>2026-08-03T22:31:50-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-mission-timeline-plan.xlsx
+++ b/docs/StructureDefinition-mission-timeline-plan.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4329" uniqueCount="615">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4330" uniqueCount="616">
   <si>
     <t>Property</t>
   </si>
@@ -27,13 +27,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://mitre.org/fhir/space-health/StructureDefinition/mission-timeline-plan</t>
+    <t>https://awatson1978.github.io/aerospace-medicine-ig/StructureDefinition/mission-timeline-plan</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.2</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T22:31:50-05:00</t>
+    <t>2026-09-02T13:24:45-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -91,6 +91,9 @@
   </si>
   <si>
     <t>Copyright</t>
+  </si>
+  <si>
+    <t>Copyright 2022-2026 The MITRE Corporation and Abigail Watson. Licensed under Creative Commons Attribution-NoDerivatives 4.0 International (CC BY-ND 4.0). Approved for Public Release; Distribution Unlimited. Public Release Case Number 25-1124.</t>
   </si>
   <si>
     <t>FHIR Version</t>
@@ -449,7 +452,7 @@
     <t>missionContext</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.org/fhir/uv/aerospace/StructureDefinition/mission-context}
+    <t xml:space="preserve">Extension {https://awatson1978.github.io/aerospace-medicine-ig/StructureDefinition/mission-context}
 </t>
   </si>
   <si>
@@ -2170,54 +2173,56 @@
       <c r="A14" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="B14" s="2"/>
+      <c r="B14" t="s" s="2">
+        <v>25</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -2240,7 +2245,7 @@
     <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="64.3359375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="81.42578125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2273,132 +2278,132 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G1" t="s" s="1">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H1" t="s" s="1">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I1" t="s" s="1">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J1" t="s" s="1">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K1" t="s" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L1" t="s" s="1">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M1" t="s" s="1">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N1" t="s" s="1">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O1" t="s" s="1">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="P1" t="s" s="1">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q1" t="s" s="1">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R1" t="s" s="1">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="S1" t="s" s="1">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="T1" t="s" s="1">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="U1" t="s" s="1">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="V1" t="s" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="W1" t="s" s="1">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="X1" t="s" s="1">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Y1" t="s" s="1">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Z1" t="s" s="1">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AA1" t="s" s="1">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AB1" t="s" s="1">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AC1" t="s" s="1">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AD1" t="s" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AE1" t="s" s="1">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AF1" t="s" s="1">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AG1" t="s" s="1">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AH1" t="s" s="1">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AI1" t="s" s="1">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ1" t="s" s="1">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AK1" t="s" s="1">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AL1" t="s" s="1">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AM1" t="s" s="1">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AN1" t="s" s="1">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
@@ -2406,10 +2411,10 @@
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H2" t="s" s="2">
         <v>20</v>
@@ -2421,13 +2426,13 @@
         <v>20</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
@@ -2478,22 +2483,22 @@
         <v>20</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI2" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AL2" t="s" s="2">
         <v>20</v>
@@ -2502,15 +2507,15 @@
         <v>20</v>
       </c>
       <c r="AN2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -2518,10 +2523,10 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>20</v>
@@ -2530,19 +2535,19 @@
         <v>20</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2592,13 +2597,13 @@
         <v>20</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>20</v>
@@ -2621,10 +2626,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2632,10 +2637,10 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>20</v>
@@ -2644,16 +2649,16 @@
         <v>20</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2704,19 +2709,19 @@
         <v>20</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>20</v>
@@ -2733,10 +2738,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2744,31 +2749,31 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2818,19 +2823,19 @@
         <v>20</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>20</v>
@@ -2847,10 +2852,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2858,10 +2863,10 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>20</v>
@@ -2873,16 +2878,16 @@
         <v>20</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2908,13 +2913,13 @@
         <v>20</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>20</v>
@@ -2932,19 +2937,19 @@
         <v>20</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>20</v>
@@ -2961,21 +2966,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>20</v>
@@ -2987,16 +2992,16 @@
         <v>20</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -3046,19 +3051,19 @@
         <v>20</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>20</v>
@@ -3070,26 +3075,26 @@
         <v>20</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>20</v>
@@ -3101,16 +3106,16 @@
         <v>20</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -3160,13 +3165,13 @@
         <v>20</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>20</v>
@@ -3184,15 +3189,15 @@
         <v>20</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -3200,10 +3205,10 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>20</v>
@@ -3215,13 +3220,13 @@
         <v>20</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -3260,29 +3265,29 @@
         <v>20</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>20</v>
@@ -3299,26 +3304,26 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>20</v>
@@ -3327,13 +3332,13 @@
         <v>20</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -3384,19 +3389,19 @@
         <v>20</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>20</v>
@@ -3413,45 +3418,45 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>20</v>
@@ -3500,19 +3505,19 @@
         <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>20</v>
@@ -3524,15 +3529,15 @@
         <v>20</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3540,10 +3545,10 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>20</v>
@@ -3552,22 +3557,22 @@
         <v>20</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>20</v>
@@ -3616,25 +3621,25 @@
         <v>20</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>20</v>
@@ -3645,10 +3650,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3656,10 +3661,10 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>20</v>
@@ -3668,22 +3673,22 @@
         <v>20</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="O13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>20</v>
@@ -3732,28 +3737,28 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="AG13" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH13" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI13" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ13" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK13" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AL13" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="AG13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH13" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ13" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AK13" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="AL13" t="s" s="2">
-        <v>156</v>
-      </c>
       <c r="AM13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>20</v>
@@ -3761,10 +3766,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3772,10 +3777,10 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>20</v>
@@ -3784,19 +3789,19 @@
         <v>20</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3846,25 +3851,25 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>20</v>
@@ -3875,10 +3880,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3886,10 +3891,10 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>20</v>
@@ -3898,22 +3903,22 @@
         <v>20</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>20</v>
@@ -3962,19 +3967,19 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>20</v>
@@ -3991,10 +3996,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -4002,31 +4007,31 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4076,22 +4081,22 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>20</v>
@@ -4105,10 +4110,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4116,10 +4121,10 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>20</v>
@@ -4131,13 +4136,13 @@
         <v>20</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4188,19 +4193,19 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>20</v>
@@ -4217,10 +4222,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4228,28 +4233,28 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4276,13 +4281,13 @@
         <v>20</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>20</v>
@@ -4300,19 +4305,19 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>20</v>
@@ -4329,10 +4334,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4340,10 +4345,10 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>20</v>
@@ -4355,13 +4360,13 @@
         <v>20</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4412,13 +4417,13 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>20</v>
@@ -4436,26 +4441,26 @@
         <v>20</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>20</v>
@@ -4467,16 +4472,16 @@
         <v>20</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4514,31 +4519,31 @@
         <v>20</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>20</v>
@@ -4550,15 +4555,15 @@
         <v>20</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4566,10 +4571,10 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>20</v>
@@ -4578,22 +4583,22 @@
         <v>20</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>20</v>
@@ -4642,19 +4647,19 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>20</v>
@@ -4666,15 +4671,15 @@
         <v>20</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4682,10 +4687,10 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>20</v>
@@ -4697,13 +4702,13 @@
         <v>20</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4754,13 +4759,13 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>20</v>
@@ -4778,26 +4783,26 @@
         <v>20</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>20</v>
@@ -4809,16 +4814,16 @@
         <v>20</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4856,31 +4861,31 @@
         <v>20</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>20</v>
@@ -4892,15 +4897,15 @@
         <v>20</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4908,10 +4913,10 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>20</v>
@@ -4920,22 +4925,22 @@
         <v>20</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>20</v>
@@ -4945,7 +4950,7 @@
         <v>20</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>20</v>
@@ -4984,19 +4989,19 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>20</v>
@@ -5008,15 +5013,15 @@
         <v>20</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5024,10 +5029,10 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>20</v>
@@ -5036,19 +5041,19 @@
         <v>20</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -5098,19 +5103,19 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>20</v>
@@ -5122,15 +5127,15 @@
         <v>20</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5138,10 +5143,10 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>20</v>
@@ -5150,20 +5155,20 @@
         <v>20</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>20</v>
@@ -5173,7 +5178,7 @@
         <v>20</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="T26" t="s" s="2">
         <v>20</v>
@@ -5212,19 +5217,19 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>20</v>
@@ -5236,15 +5241,15 @@
         <v>20</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5252,10 +5257,10 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>20</v>
@@ -5264,20 +5269,20 @@
         <v>20</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>20</v>
@@ -5326,19 +5331,19 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>20</v>
@@ -5350,15 +5355,15 @@
         <v>20</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5366,10 +5371,10 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>20</v>
@@ -5378,22 +5383,22 @@
         <v>20</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>20</v>
@@ -5442,19 +5447,19 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>20</v>
@@ -5466,15 +5471,15 @@
         <v>20</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5482,10 +5487,10 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>20</v>
@@ -5494,22 +5499,22 @@
         <v>20</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>20</v>
@@ -5558,19 +5563,19 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>20</v>
@@ -5582,15 +5587,15 @@
         <v>20</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5598,31 +5603,31 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5648,13 +5653,13 @@
         <v>20</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>20</v>
@@ -5672,25 +5677,25 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>20</v>
@@ -5701,10 +5706,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5712,10 +5717,10 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>20</v>
@@ -5724,22 +5729,22 @@
         <v>20</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>20</v>
@@ -5788,25 +5793,25 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>20</v>
@@ -5817,10 +5822,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5828,10 +5833,10 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>20</v>
@@ -5843,13 +5848,13 @@
         <v>20</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5857,7 +5862,7 @@
         <v>20</v>
       </c>
       <c r="Q32" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="R32" t="s" s="2">
         <v>20</v>
@@ -5878,13 +5883,13 @@
         <v>20</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>20</v>
@@ -5902,22 +5907,22 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>20</v>
@@ -5931,21 +5936,21 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>20</v>
@@ -5954,19 +5959,19 @@
         <v>20</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -6016,25 +6021,25 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>20</v>
@@ -6045,10 +6050,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6056,10 +6061,10 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>20</v>
@@ -6068,22 +6073,22 @@
         <v>20</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>20</v>
@@ -6132,25 +6137,25 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>20</v>
@@ -6161,10 +6166,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6172,10 +6177,10 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>20</v>
@@ -6184,19 +6189,19 @@
         <v>20</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6246,22 +6251,22 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>20</v>
@@ -6275,10 +6280,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6286,31 +6291,31 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6360,22 +6365,22 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>20</v>
@@ -6389,10 +6394,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6400,10 +6405,10 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>20</v>
@@ -6412,22 +6417,22 @@
         <v>20</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>20</v>
@@ -6476,22 +6481,22 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>20</v>
@@ -6505,10 +6510,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6516,10 +6521,10 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>20</v>
@@ -6528,19 +6533,19 @@
         <v>20</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6566,13 +6571,13 @@
         <v>20</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>20</v>
@@ -6590,22 +6595,22 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>20</v>
@@ -6619,10 +6624,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6630,10 +6635,10 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>20</v>
@@ -6645,16 +6650,16 @@
         <v>20</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6704,28 +6709,28 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>20</v>
@@ -6733,10 +6738,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6744,10 +6749,10 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>20</v>
@@ -6759,13 +6764,13 @@
         <v>20</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6816,19 +6821,19 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>20</v>
@@ -6845,21 +6850,21 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>20</v>
@@ -6871,17 +6876,17 @@
         <v>20</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>20</v>
@@ -6930,28 +6935,28 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>20</v>
@@ -6959,10 +6964,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6970,10 +6975,10 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>20</v>
@@ -6985,16 +6990,16 @@
         <v>20</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7044,28 +7049,28 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>20</v>
@@ -7073,10 +7078,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7084,10 +7089,10 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>20</v>
@@ -7099,19 +7104,19 @@
         <v>20</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>20</v>
@@ -7160,28 +7165,28 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>20</v>
@@ -7189,10 +7194,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7200,10 +7205,10 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>20</v>
@@ -7212,22 +7217,22 @@
         <v>20</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>20</v>
@@ -7276,28 +7281,28 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>20</v>
@@ -7305,10 +7310,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7316,10 +7321,10 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>20</v>
@@ -7331,17 +7336,17 @@
         <v>20</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>20</v>
@@ -7366,13 +7371,13 @@
         <v>20</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>20</v>
@@ -7390,22 +7395,22 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>20</v>
@@ -7419,10 +7424,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7430,10 +7435,10 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>20</v>
@@ -7445,13 +7450,13 @@
         <v>20</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7502,19 +7507,19 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>20</v>
@@ -7526,15 +7531,15 @@
         <v>20</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7542,10 +7547,10 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>20</v>
@@ -7557,13 +7562,13 @@
         <v>20</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7614,19 +7619,19 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>20</v>
@@ -7643,10 +7648,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7654,10 +7659,10 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>20</v>
@@ -7669,13 +7674,13 @@
         <v>20</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7726,19 +7731,19 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>20</v>
@@ -7750,15 +7755,15 @@
         <v>20</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7766,10 +7771,10 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>20</v>
@@ -7781,13 +7786,13 @@
         <v>20</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7838,39 +7843,39 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN49" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="AG49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ49" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AK49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>371</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7878,10 +7883,10 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>20</v>
@@ -7893,19 +7898,19 @@
         <v>20</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>20</v>
@@ -7954,19 +7959,19 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>20</v>
@@ -7983,10 +7988,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7994,10 +7999,10 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>20</v>
@@ -8009,13 +8014,13 @@
         <v>20</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8066,19 +8071,19 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>20</v>
@@ -8095,10 +8100,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8106,10 +8111,10 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>20</v>
@@ -8121,17 +8126,17 @@
         <v>20</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>20</v>
@@ -8180,19 +8185,19 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>20</v>
@@ -8209,10 +8214,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8220,10 +8225,10 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>20</v>
@@ -8235,13 +8240,13 @@
         <v>20</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8292,13 +8297,13 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>20</v>
@@ -8316,26 +8321,26 @@
         <v>20</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>20</v>
@@ -8347,16 +8352,16 @@
         <v>20</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8406,19 +8411,19 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>20</v>
@@ -8430,50 +8435,50 @@
         <v>20</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>20</v>
@@ -8522,19 +8527,19 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>20</v>
@@ -8546,15 +8551,15 @@
         <v>20</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8562,10 +8567,10 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>20</v>
@@ -8577,13 +8582,13 @@
         <v>20</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8610,13 +8615,13 @@
         <v>20</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>20</v>
@@ -8634,19 +8639,19 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>20</v>
@@ -8663,10 +8668,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8674,10 +8679,10 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>20</v>
@@ -8689,16 +8694,16 @@
         <v>20</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8724,13 +8729,13 @@
         <v>20</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>20</v>
@@ -8748,19 +8753,19 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>20</v>
@@ -8777,10 +8782,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8788,10 +8793,10 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>20</v>
@@ -8803,13 +8808,13 @@
         <v>20</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8836,13 +8841,13 @@
         <v>20</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>20</v>
@@ -8860,19 +8865,19 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>20</v>
@@ -8889,10 +8894,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8900,10 +8905,10 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>20</v>
@@ -8915,13 +8920,13 @@
         <v>20</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8948,13 +8953,13 @@
         <v>20</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>20</v>
@@ -8972,19 +8977,19 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>20</v>
@@ -9001,10 +9006,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9012,10 +9017,10 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>20</v>
@@ -9027,13 +9032,13 @@
         <v>20</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9060,13 +9065,13 @@
         <v>20</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>20</v>
@@ -9084,19 +9089,19 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>20</v>
@@ -9113,10 +9118,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9124,10 +9129,10 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>20</v>
@@ -9139,13 +9144,13 @@
         <v>20</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9196,19 +9201,19 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>20</v>
@@ -9225,10 +9230,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9236,10 +9241,10 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>20</v>
@@ -9251,13 +9256,13 @@
         <v>20</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9308,19 +9313,19 @@
         <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>20</v>
@@ -9337,10 +9342,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9348,10 +9353,10 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>20</v>
@@ -9363,13 +9368,13 @@
         <v>20</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9420,13 +9425,13 @@
         <v>20</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>20</v>
@@ -9444,26 +9449,26 @@
         <v>20</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>20</v>
@@ -9475,16 +9480,16 @@
         <v>20</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9534,19 +9539,19 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>20</v>
@@ -9558,50 +9563,50 @@
         <v>20</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>20</v>
@@ -9650,19 +9655,19 @@
         <v>20</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>20</v>
@@ -9674,15 +9679,15 @@
         <v>20</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9690,10 +9695,10 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>20</v>
@@ -9705,13 +9710,13 @@
         <v>20</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9738,13 +9743,13 @@
         <v>20</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>20</v>
@@ -9762,19 +9767,19 @@
         <v>20</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>20</v>
@@ -9791,10 +9796,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9802,10 +9807,10 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>20</v>
@@ -9817,13 +9822,13 @@
         <v>20</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9874,19 +9879,19 @@
         <v>20</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>20</v>
@@ -9903,10 +9908,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9914,10 +9919,10 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>20</v>
@@ -9929,13 +9934,13 @@
         <v>20</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9986,19 +9991,19 @@
         <v>20</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>20</v>
@@ -10015,10 +10020,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10026,13 +10031,13 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>20</v>
@@ -10041,16 +10046,16 @@
         <v>20</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10100,22 +10105,22 @@
         <v>20</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>20</v>
@@ -10129,10 +10134,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10140,10 +10145,10 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>20</v>
@@ -10155,13 +10160,13 @@
         <v>20</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10212,13 +10217,13 @@
         <v>20</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>20</v>
@@ -10236,26 +10241,26 @@
         <v>20</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>20</v>
@@ -10267,16 +10272,16 @@
         <v>20</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10326,19 +10331,19 @@
         <v>20</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>20</v>
@@ -10350,50 +10355,50 @@
         <v>20</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I72" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>20</v>
@@ -10442,19 +10447,19 @@
         <v>20</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG72" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>20</v>
@@ -10466,15 +10471,15 @@
         <v>20</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10482,10 +10487,10 @@
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>20</v>
@@ -10497,13 +10502,13 @@
         <v>20</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10554,19 +10559,19 @@
         <v>20</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>20</v>
@@ -10583,10 +10588,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10594,13 +10599,13 @@
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H74" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I74" t="s" s="2">
         <v>20</v>
@@ -10609,13 +10614,13 @@
         <v>20</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10666,22 +10671,22 @@
         <v>20</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AG74" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AL74" t="s" s="2">
         <v>20</v>
@@ -10695,10 +10700,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10706,13 +10711,13 @@
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H75" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I75" t="s" s="2">
         <v>20</v>
@@ -10721,13 +10726,13 @@
         <v>20</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10778,22 +10783,22 @@
         <v>20</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AL75" t="s" s="2">
         <v>20</v>
@@ -10807,10 +10812,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10818,10 +10823,10 @@
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>20</v>
@@ -10833,13 +10838,13 @@
         <v>20</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -10890,22 +10895,22 @@
         <v>20</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG76" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AL76" t="s" s="2">
         <v>20</v>
@@ -10919,10 +10924,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10930,10 +10935,10 @@
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>20</v>
@@ -10945,13 +10950,13 @@
         <v>20</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -10978,13 +10983,13 @@
         <v>20</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>20</v>
@@ -11002,19 +11007,19 @@
         <v>20</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG77" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>20</v>
@@ -11031,10 +11036,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11042,10 +11047,10 @@
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>20</v>
@@ -11057,13 +11062,13 @@
         <v>20</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11114,19 +11119,19 @@
         <v>20</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG78" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>20</v>
@@ -11143,10 +11148,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11154,10 +11159,10 @@
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>20</v>
@@ -11169,16 +11174,16 @@
         <v>20</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11228,19 +11233,19 @@
         <v>20</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AG79" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>20</v>
@@ -11257,10 +11262,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11268,10 +11273,10 @@
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>20</v>
@@ -11283,13 +11288,13 @@
         <v>20</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11340,19 +11345,19 @@
         <v>20</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AG80" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>20</v>
@@ -11369,10 +11374,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11380,10 +11385,10 @@
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>20</v>
@@ -11395,13 +11400,13 @@
         <v>20</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -11452,19 +11457,19 @@
         <v>20</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AG81" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>20</v>
@@ -11481,10 +11486,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11492,10 +11497,10 @@
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>20</v>
@@ -11507,85 +11512,85 @@
         <v>20</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="O82" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="P82" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q82" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="R82" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S82" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T82" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U82" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V82" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W82" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X82" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="Z82" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF82" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="M82" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="P82" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q82" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="R82" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S82" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T82" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U82" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V82" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W82" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X82" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="Y82" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="Z82" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="AA82" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB82" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC82" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD82" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE82" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF82" t="s" s="2">
-        <v>483</v>
-      </c>
       <c r="AG82" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AL82" t="s" s="2">
         <v>20</v>
@@ -11599,10 +11604,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11610,10 +11615,10 @@
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>20</v>
@@ -11625,13 +11630,13 @@
         <v>20</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -11682,19 +11687,19 @@
         <v>20</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AG83" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>20</v>
@@ -11711,10 +11716,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11722,10 +11727,10 @@
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>20</v>
@@ -11737,16 +11742,16 @@
         <v>20</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -11796,19 +11801,19 @@
         <v>20</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AG84" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>20</v>
@@ -11825,10 +11830,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11836,10 +11841,10 @@
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>20</v>
@@ -11851,13 +11856,13 @@
         <v>20</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -11908,13 +11913,13 @@
         <v>20</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG85" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>20</v>
@@ -11932,26 +11937,26 @@
         <v>20</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>20</v>
@@ -11963,16 +11968,16 @@
         <v>20</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -12022,19 +12027,19 @@
         <v>20</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG86" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>20</v>
@@ -12046,50 +12051,50 @@
         <v>20</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I87" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>20</v>
@@ -12138,19 +12143,19 @@
         <v>20</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG87" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>20</v>
@@ -12162,15 +12167,15 @@
         <v>20</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12178,10 +12183,10 @@
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>20</v>
@@ -12193,16 +12198,16 @@
         <v>20</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -12228,13 +12233,13 @@
         <v>20</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>20</v>
@@ -12252,19 +12257,19 @@
         <v>20</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AG88" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>20</v>
@@ -12281,10 +12286,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12292,10 +12297,10 @@
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>20</v>
@@ -12307,16 +12312,16 @@
         <v>20</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -12366,19 +12371,19 @@
         <v>20</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AG89" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>20</v>
@@ -12395,10 +12400,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12406,10 +12411,10 @@
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>20</v>
@@ -12421,13 +12426,13 @@
         <v>20</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -12478,19 +12483,19 @@
         <v>20</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AG90" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>20</v>
@@ -12507,10 +12512,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12518,10 +12523,10 @@
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>20</v>
@@ -12533,13 +12538,13 @@
         <v>20</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -12590,19 +12595,19 @@
         <v>20</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AG91" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>20</v>
@@ -12619,10 +12624,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12630,10 +12635,10 @@
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>20</v>
@@ -12645,16 +12650,16 @@
         <v>20</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -12704,19 +12709,19 @@
         <v>20</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AG92" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>20</v>
@@ -12733,10 +12738,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12744,10 +12749,10 @@
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>20</v>
@@ -12759,13 +12764,13 @@
         <v>20</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -12816,13 +12821,13 @@
         <v>20</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG93" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>20</v>
@@ -12840,26 +12845,26 @@
         <v>20</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>20</v>
@@ -12871,16 +12876,16 @@
         <v>20</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -12930,19 +12935,19 @@
         <v>20</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG94" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>20</v>
@@ -12954,50 +12959,50 @@
         <v>20</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I95" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>20</v>
@@ -13046,19 +13051,19 @@
         <v>20</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG95" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>20</v>
@@ -13070,15 +13075,15 @@
         <v>20</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13086,10 +13091,10 @@
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>20</v>
@@ -13101,13 +13106,13 @@
         <v>20</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -13158,19 +13163,19 @@
         <v>20</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AG96" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>20</v>
@@ -13187,10 +13192,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13198,10 +13203,10 @@
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>20</v>
@@ -13213,13 +13218,13 @@
         <v>20</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -13246,13 +13251,13 @@
         <v>20</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>20</v>
@@ -13270,19 +13275,19 @@
         <v>20</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AG97" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>20</v>
@@ -13299,10 +13304,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13310,10 +13315,10 @@
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>20</v>
@@ -13325,13 +13330,13 @@
         <v>20</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -13382,19 +13387,19 @@
         <v>20</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AG98" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>20</v>
@@ -13411,10 +13416,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13422,10 +13427,10 @@
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>20</v>
@@ -13437,13 +13442,13 @@
         <v>20</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -13494,19 +13499,19 @@
         <v>20</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AG99" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>20</v>
@@ -13523,10 +13528,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13534,10 +13539,10 @@
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>20</v>
@@ -13549,13 +13554,13 @@
         <v>20</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -13606,19 +13611,19 @@
         <v>20</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AG100" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>20</v>
@@ -13635,10 +13640,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13646,10 +13651,10 @@
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>20</v>
@@ -13661,13 +13666,13 @@
         <v>20</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -13718,13 +13723,13 @@
         <v>20</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG101" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>20</v>
@@ -13742,26 +13747,26 @@
         <v>20</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H102" t="s" s="2">
         <v>20</v>
@@ -13773,16 +13778,16 @@
         <v>20</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -13832,19 +13837,19 @@
         <v>20</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG102" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>20</v>
@@ -13856,50 +13861,50 @@
         <v>20</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I103" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>20</v>
@@ -13948,19 +13953,19 @@
         <v>20</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG103" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI103" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>20</v>
@@ -13972,15 +13977,15 @@
         <v>20</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -13988,10 +13993,10 @@
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H104" t="s" s="2">
         <v>20</v>
@@ -14003,13 +14008,13 @@
         <v>20</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -14036,13 +14041,13 @@
         <v>20</v>
       </c>
       <c r="X104" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>20</v>
@@ -14060,19 +14065,19 @@
         <v>20</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AG104" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI104" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>20</v>
@@ -14089,10 +14094,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14100,10 +14105,10 @@
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>20</v>
@@ -14115,13 +14120,13 @@
         <v>20</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -14148,13 +14153,13 @@
         <v>20</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>20</v>
@@ -14172,19 +14177,19 @@
         <v>20</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AG105" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI105" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK105" t="s" s="2">
         <v>20</v>
@@ -14201,10 +14206,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14212,10 +14217,10 @@
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>20</v>
@@ -14227,13 +14232,13 @@
         <v>20</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -14260,13 +14265,13 @@
         <v>20</v>
       </c>
       <c r="X106" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Y106" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="Z106" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>20</v>
@@ -14284,19 +14289,19 @@
         <v>20</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AG106" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>20</v>
@@ -14313,10 +14318,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14324,10 +14329,10 @@
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H107" t="s" s="2">
         <v>20</v>
@@ -14339,13 +14344,13 @@
         <v>20</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -14372,13 +14377,13 @@
         <v>20</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>20</v>
@@ -14396,19 +14401,19 @@
         <v>20</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AG107" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI107" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>20</v>
@@ -14425,10 +14430,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14436,10 +14441,10 @@
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G108" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H108" t="s" s="2">
         <v>20</v>
@@ -14451,13 +14456,13 @@
         <v>20</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -14484,13 +14489,13 @@
         <v>20</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>20</v>
@@ -14508,19 +14513,19 @@
         <v>20</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AG108" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH108" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI108" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK108" t="s" s="2">
         <v>20</v>
@@ -14537,10 +14542,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14548,10 +14553,10 @@
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H109" t="s" s="2">
         <v>20</v>
@@ -14563,13 +14568,13 @@
         <v>20</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -14596,13 +14601,13 @@
         <v>20</v>
       </c>
       <c r="X109" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Y109" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="Z109" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>20</v>
@@ -14620,19 +14625,19 @@
         <v>20</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AG109" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI109" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK109" t="s" s="2">
         <v>20</v>
@@ -14649,10 +14654,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14660,10 +14665,10 @@
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H110" t="s" s="2">
         <v>20</v>
@@ -14675,13 +14680,13 @@
         <v>20</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -14708,13 +14713,13 @@
         <v>20</v>
       </c>
       <c r="X110" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="Z110" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>20</v>
@@ -14732,19 +14737,19 @@
         <v>20</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AG110" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI110" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK110" t="s" s="2">
         <v>20</v>
@@ -14761,10 +14766,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14772,10 +14777,10 @@
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H111" t="s" s="2">
         <v>20</v>
@@ -14787,13 +14792,13 @@
         <v>20</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -14820,13 +14825,13 @@
         <v>20</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>20</v>
@@ -14844,19 +14849,19 @@
         <v>20</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AG111" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI111" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK111" t="s" s="2">
         <v>20</v>
@@ -14873,10 +14878,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -14884,10 +14889,10 @@
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G112" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H112" t="s" s="2">
         <v>20</v>
@@ -14899,16 +14904,16 @@
         <v>20</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -14958,22 +14963,22 @@
         <v>20</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AG112" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI112" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AL112" t="s" s="2">
         <v>20</v>
@@ -14987,10 +14992,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -14998,10 +15003,10 @@
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H113" t="s" s="2">
         <v>20</v>
@@ -15013,16 +15018,16 @@
         <v>20</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -15072,19 +15077,19 @@
         <v>20</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AG113" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI113" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK113" t="s" s="2">
         <v>20</v>
@@ -15101,10 +15106,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15112,10 +15117,10 @@
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H114" t="s" s="2">
         <v>20</v>
@@ -15127,16 +15132,16 @@
         <v>20</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -15186,19 +15191,19 @@
         <v>20</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AG114" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI114" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK114" t="s" s="2">
         <v>20</v>
@@ -15215,10 +15220,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15226,10 +15231,10 @@
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G115" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H115" t="s" s="2">
         <v>20</v>
@@ -15241,13 +15246,13 @@
         <v>20</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -15298,13 +15303,13 @@
         <v>20</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG115" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH115" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI115" t="s" s="2">
         <v>20</v>
@@ -15322,26 +15327,26 @@
         <v>20</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G116" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H116" t="s" s="2">
         <v>20</v>
@@ -15353,16 +15358,16 @@
         <v>20</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
@@ -15412,19 +15417,19 @@
         <v>20</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG116" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH116" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI116" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AK116" t="s" s="2">
         <v>20</v>
@@ -15436,50 +15441,50 @@
         <v>20</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G117" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H117" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I117" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J117" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O117" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>20</v>
@@ -15528,19 +15533,19 @@
         <v>20</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG117" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH117" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI117" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AK117" t="s" s="2">
         <v>20</v>
@@ -15552,15 +15557,15 @@
         <v>20</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -15568,10 +15573,10 @@
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G118" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H118" t="s" s="2">
         <v>20</v>
@@ -15583,16 +15588,16 @@
         <v>20</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
@@ -15642,19 +15647,19 @@
         <v>20</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AG118" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH118" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI118" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK118" t="s" s="2">
         <v>20</v>
@@ -15671,10 +15676,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -15682,10 +15687,10 @@
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G119" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H119" t="s" s="2">
         <v>20</v>
@@ -15697,16 +15702,16 @@
         <v>20</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
@@ -15756,19 +15761,19 @@
         <v>20</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AG119" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH119" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI119" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ119" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK119" t="s" s="2">
         <v>20</v>
@@ -15785,10 +15790,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -15796,10 +15801,10 @@
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G120" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H120" t="s" s="2">
         <v>20</v>
@@ -15811,13 +15816,13 @@
         <v>20</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -15868,22 +15873,22 @@
         <v>20</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AG120" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH120" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI120" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ120" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AL120" t="s" s="2">
         <v>20</v>
